--- a/measurements/33/Filled_2D_sections/axial/week33_axial_Batch_Allmarks.xlsx
+++ b/measurements/33/Filled_2D_sections/axial/week33_axial_Batch_Allmarks.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:AK32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,12 +487,122 @@
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v3_mm</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_min_mm</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_max_mm</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_mean_mm</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
@@ -506,43 +616,79 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>11.098750743605</v>
+        <v>4230.612244897959</v>
       </c>
       <c r="D2" t="n">
-        <v>24.3150210235177</v>
+        <v>474.7218390305837</v>
       </c>
       <c r="E2" t="n">
-        <v>14.75572788424608</v>
+        <v>288.0880205971854</v>
       </c>
       <c r="F2" t="n">
-        <v>1.647836095532608</v>
+        <v>1.647836095532609</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2359036515071878</v>
+        <v>0.2359036515071877</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5255335365853658</v>
+        <v>2.191220238095238</v>
       </c>
       <c r="J2" t="n">
-        <v>1.292682926829268</v>
+        <v>25.23809523809524</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7785823170731707</v>
-      </c>
-      <c r="N2" t="inlineStr">
+        <v>8.065137987012987</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M2" t="n">
+        <v>25.23809523809524</v>
+      </c>
+      <c r="N2" t="n">
+        <v>13.98623511904762</v>
+      </c>
+      <c r="S2" t="n">
+        <v>6</v>
+      </c>
+      <c r="W2" t="n">
+        <v>4.951636904761904</v>
+      </c>
+      <c r="X2" t="n">
+        <v>11.3188244047619</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>7.041480654761904</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.548363095238095</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2.503720238095238</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.191220238095238</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>11.26714753123141</v>
+      <c r="AK2" s="2" t="n">
+        <v>4294.801587301587</v>
       </c>
     </row>
     <row r="3">
@@ -553,17 +699,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11.06722189173111</v>
+        <v>4218.594104308389</v>
       </c>
       <c r="D3" t="n">
-        <v>24.79445649647131</v>
+        <v>484.0822458834875</v>
       </c>
       <c r="E3" t="n">
-        <v>14.84246807563596</v>
+        <v>289.7815195719401</v>
       </c>
       <c r="F3" t="n">
         <v>1.670507652104816</v>
@@ -572,24 +718,57 @@
         <v>0.2262243222346011</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5256288109756098</v>
+        <v>2.938988095238095</v>
       </c>
       <c r="J3" t="n">
-        <v>1.268292682926829</v>
+        <v>24.76190476190476</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7885861280487805</v>
-      </c>
-      <c r="N3" t="inlineStr">
+        <v>9.054315476190476</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>24.76190476190476</v>
+      </c>
+      <c r="N3" t="n">
+        <v>14.05133928571428</v>
+      </c>
+      <c r="S3" t="n">
+        <v>6</v>
+      </c>
+      <c r="W3" t="n">
+        <v>4.575892857142857</v>
+      </c>
+      <c r="X3" t="n">
+        <v>12.50930059523809</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>7.502170138888888</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>3.777901785714286</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2.938988095238095</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>perimeter</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>22.56352515409633</v>
+      <c r="AK3" s="2" t="n">
+        <v>440.5259672942615</v>
       </c>
     </row>
     <row r="4">
@@ -600,17 +779,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11.0434265318263</v>
+        <v>4209.523809523809</v>
       </c>
       <c r="D4" t="n">
-        <v>24.06765185623634</v>
+        <v>469.892250526519</v>
       </c>
       <c r="E4" t="n">
-        <v>14.80797505669478</v>
+        <v>289.1080844402313</v>
       </c>
       <c r="F4" t="n">
         <v>1.625316882564251</v>
@@ -619,24 +798,63 @@
         <v>0.2395776325074515</v>
       </c>
       <c r="H4" t="n">
+        <v>10</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.903645833333333</v>
+      </c>
+      <c r="J4" t="n">
+        <v>24.76190476190476</v>
+      </c>
+      <c r="K4" t="n">
+        <v>9.036458333333332</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" t="n">
+        <v>24.76190476190476</v>
+      </c>
+      <c r="N4" t="n">
+        <v>14.02529761904762</v>
+      </c>
+      <c r="O4" t="n">
+        <v>13.54352678571428</v>
+      </c>
+      <c r="S4" t="n">
         <v>4</v>
       </c>
-      <c r="I4" t="n">
-        <v>0.5630716463414634</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.268292682926829</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.8108565167682927</v>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="W4" t="n">
+        <v>4.536830357142857</v>
+      </c>
+      <c r="X4" t="n">
+        <v>10.99330357142857</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>7.092168898809524</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>3.011532738095238</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.903645833333333</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>perimeter_convex</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>14.44614510579807</v>
+      <c r="AK4" s="2" t="n">
+        <v>282.0437853989147</v>
       </c>
     </row>
     <row r="5">
@@ -647,17 +865,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11.03955978584176</v>
+        <v>4208.049886621315</v>
       </c>
       <c r="D5" t="n">
-        <v>24.6185246909537</v>
+        <v>480.6473868233817</v>
       </c>
       <c r="E5" t="n">
-        <v>14.83063194228382</v>
+        <v>289.5504331588745</v>
       </c>
       <c r="F5" t="n">
         <v>1.659978130855199</v>
@@ -666,23 +884,62 @@
         <v>0.2288956676605705</v>
       </c>
       <c r="H5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.241443452380952</v>
+      </c>
+      <c r="J5" t="n">
+        <v>24.76190476190476</v>
+      </c>
+      <c r="K5" t="n">
+        <v>9.153459821428569</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>24.76190476190476</v>
+      </c>
+      <c r="N5" t="n">
+        <v>15.56547619047619</v>
+      </c>
+      <c r="O5" t="n">
+        <v>14.05133928571428</v>
+      </c>
+      <c r="S5" t="n">
         <v>4</v>
       </c>
-      <c r="I5" t="n">
-        <v>0.5547827743902439</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1.268292682926829</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.8350085746951219</v>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="W5" t="n">
+        <v>4.540550595238095</v>
+      </c>
+      <c r="X5" t="n">
+        <v>10.83147321428571</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>7.043805803571427</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.502604166666667</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>3.236607142857143</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.241443452380952</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>LGI</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="AK5" s="2" t="n">
         <v>1.56005955253642</v>
       </c>
     </row>
@@ -694,42 +951,78 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11.07584770969661</v>
+        <v>4221.8820861678</v>
       </c>
       <c r="D6" t="n">
-        <v>26.06029783516395</v>
+        <v>508.7962910674867</v>
       </c>
       <c r="E6" t="n">
-        <v>14.77593342269339</v>
+        <v>288.4825096811567</v>
       </c>
       <c r="F6" t="n">
         <v>1.763698921053586</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2049406409111946</v>
+        <v>0.2049406409111947</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5691692073170732</v>
+        <v>1.365327380952381</v>
       </c>
       <c r="J6" t="n">
-        <v>1.284775152439025</v>
+        <v>25.08370535714285</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8362804878048781</v>
-      </c>
-      <c r="N6" t="inlineStr">
+        <v>8.66024925595238</v>
+      </c>
+      <c r="L6" t="n">
+        <v>4</v>
+      </c>
+      <c r="P6" t="n">
+        <v>14.07738095238095</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>25.08370535714285</v>
+      </c>
+      <c r="R6" t="n">
+        <v>17.63113839285714</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" t="n">
+        <v>11.11235119047619</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4.402901785714286</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.365327380952381</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>3.642113095238095</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.980530753968254</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
         <is>
           <t>Compactness</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="AK6" s="2" t="n">
         <v>0.2847204675368404</v>
       </c>
     </row>
@@ -741,17 +1034,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11.07317073170732</v>
+        <v>4220.861678004535</v>
       </c>
       <c r="D7" t="n">
-        <v>25.66066914942207</v>
+        <v>500.9940167268117</v>
       </c>
       <c r="E7" t="n">
-        <v>14.79859030246735</v>
+        <v>288.9248582862672</v>
       </c>
       <c r="F7" t="n">
         <v>1.733994159237161</v>
@@ -760,24 +1053,57 @@
         <v>0.2113225807057277</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5786966463414634</v>
+        <v>1.742931547619047</v>
       </c>
       <c r="J7" t="n">
-        <v>1.268292682926829</v>
+        <v>24.76190476190476</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8379954268292684</v>
-      </c>
-      <c r="N7" t="inlineStr">
+        <v>8.591114831349207</v>
+      </c>
+      <c r="L7" t="n">
+        <v>4</v>
+      </c>
+      <c r="P7" t="n">
+        <v>14.37313988095238</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>24.76190476190476</v>
+      </c>
+      <c r="R7" t="n">
+        <v>17.62648809523809</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>11.29836309523809</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.742931547619047</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>3.725818452380952</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>3.041294642857143</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>Sulci_count</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>3.2</v>
+      <c r="AK7" s="2" t="n">
+        <v>13.55</v>
       </c>
     </row>
     <row r="8">
@@ -788,17 +1114,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11.28673408685306</v>
+        <v>4302.267573696145</v>
       </c>
       <c r="D8" t="n">
-        <v>24.68159267379016</v>
+        <v>481.8787141073317</v>
       </c>
       <c r="E8" t="n">
-        <v>14.77001531531171</v>
+        <v>288.3669656798953</v>
       </c>
       <c r="F8" t="n">
         <v>1.671060736694251</v>
@@ -807,24 +1133,57 @@
         <v>0.2328261709128925</v>
       </c>
       <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.313244047619047</v>
+      </c>
+      <c r="J8" t="n">
+        <v>24.76190476190476</v>
+      </c>
+      <c r="K8" t="n">
+        <v>8.062686011904763</v>
+      </c>
+      <c r="L8" t="n">
         <v>4</v>
       </c>
-      <c r="I8" t="n">
-        <v>0.7347560975609756</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1.268292682926829</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.9057736280487805</v>
-      </c>
-      <c r="N8" t="inlineStr">
+      <c r="P8" t="n">
+        <v>14.34523809523809</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>24.76190476190476</v>
+      </c>
+      <c r="R8" t="n">
+        <v>17.68415178571428</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>6.158854166666666</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.313244047619047</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>3.718377976190476</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.836681547619047</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
         <is>
           <t>min_depth_mm</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>0.6628144054878049</v>
+      <c r="AK8" s="2" t="n">
+        <v>1.857793898809524</v>
       </c>
     </row>
     <row r="9">
@@ -835,43 +1194,79 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>11.33670434265318</v>
+        <v>4321.315192743764</v>
       </c>
       <c r="D9" t="n">
-        <v>23.1387918402509</v>
+        <v>451.7573645001366</v>
       </c>
       <c r="E9" t="n">
-        <v>14.80450831971518</v>
+        <v>289.0404005277724</v>
       </c>
       <c r="F9" t="n">
         <v>1.562955779452463</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2660818958747449</v>
+        <v>0.2660818958747448</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5306783536585366</v>
+        <v>1.428571428571428</v>
       </c>
       <c r="J9" t="n">
-        <v>1.268292682926829</v>
+        <v>24.76190476190476</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8315310594512195</v>
-      </c>
-      <c r="N9" t="inlineStr">
+        <v>7.206530448717948</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3</v>
+      </c>
+      <c r="M9" t="n">
+        <v>24.76190476190476</v>
+      </c>
+      <c r="N9" t="n">
+        <v>15.43154761904762</v>
+      </c>
+      <c r="O9" t="n">
+        <v>14.38430059523809</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>10.36086309523809</v>
+      </c>
+      <c r="U9" t="n">
+        <v>6.303943452380952</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.428571428571428</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>3.949032738095238</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.805292038690475</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
         <is>
           <t>max_depth_mm</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>1.400600228658537</v>
+      <c r="AK9" s="2" t="n">
+        <v>27.34505208333333</v>
       </c>
     </row>
     <row r="10">
@@ -882,43 +1277,82 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>11.48810232004759</v>
+        <v>4379.024943310657</v>
       </c>
       <c r="D10" t="n">
-        <v>24.17113088107691</v>
+        <v>471.9125552972158</v>
       </c>
       <c r="E10" t="n">
-        <v>14.42018253919555</v>
+        <v>281.5368971938178</v>
       </c>
       <c r="F10" t="n">
         <v>1.676201449973138</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2470951488370751</v>
+        <v>0.2470951488370752</v>
       </c>
       <c r="H10" t="n">
+        <v>15</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.305803571428571</v>
+      </c>
+      <c r="J10" t="n">
+        <v>25.99516369047619</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6.458209325396826</v>
+      </c>
+      <c r="L10" t="n">
         <v>3</v>
       </c>
-      <c r="I10" t="n">
-        <v>0.7420922256097561</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.331459603658537</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.9412157012195123</v>
-      </c>
-      <c r="N10" t="inlineStr">
+      <c r="M10" t="n">
+        <v>25.99516369047619</v>
+      </c>
+      <c r="N10" t="n">
+        <v>14.64471726190476</v>
+      </c>
+      <c r="O10" t="n">
+        <v>14.48846726190476</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W10" t="n">
+        <v>4.170386904761904</v>
+      </c>
+      <c r="X10" t="n">
+        <v>7.180059523809524</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>5.438988095238095</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.305803571428571</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>3.346354166666667</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.498604910714286</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
         <is>
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>0.970890259781504</v>
+      <c r="AK10" s="2" t="n">
+        <v>7.147405429405699</v>
       </c>
     </row>
     <row r="11">
@@ -929,17 +1363,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>11.59339678762641</v>
+        <v>4419.160997732426</v>
       </c>
       <c r="D11" t="n">
-        <v>22.1321557847465</v>
+        <v>432.1039938926697</v>
       </c>
       <c r="E11" t="n">
-        <v>14.69612660931378</v>
+        <v>286.9243766580309</v>
       </c>
       <c r="F11" t="n">
         <v>1.505985650036526</v>
@@ -948,16 +1382,60 @@
         <v>0.2974220255774956</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5841272865853658</v>
+        <v>1.38764880952381</v>
       </c>
       <c r="J11" t="n">
-        <v>1.355659298780488</v>
+        <v>26.46763392857143</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9032012195121951</v>
+        <v>5.835084033613445</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>26.46763392857143</v>
+      </c>
+      <c r="N11" t="n">
+        <v>15.0297619047619</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>4.376860119047619</v>
+      </c>
+      <c r="X11" t="n">
+        <v>11.40438988095238</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>6.299479166666667</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.38764880952381</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>4.109002976190476</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.62016369047619</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="AK11" s="2" t="n">
+        <v>2.55</v>
       </c>
     </row>
     <row r="12">
@@ -968,17 +1446,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>11.58209399167163</v>
+        <v>4414.85260770975</v>
       </c>
       <c r="D12" t="n">
-        <v>22.04296424621489</v>
+        <v>430.362635283243</v>
       </c>
       <c r="E12" t="n">
-        <v>14.52611289954767</v>
+        <v>283.6050613721212</v>
       </c>
       <c r="F12" t="n">
         <v>1.51747163185695</v>
@@ -987,16 +1465,60 @@
         <v>0.2995414698879267</v>
       </c>
       <c r="H12" t="n">
+        <v>16</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.38764880952381</v>
+      </c>
+      <c r="J12" t="n">
+        <v>26.96800595238095</v>
+      </c>
+      <c r="K12" t="n">
+        <v>5.931919642857141</v>
+      </c>
+      <c r="L12" t="n">
         <v>3</v>
       </c>
-      <c r="I12" t="n">
-        <v>0.6520579268292683</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1.381288109756098</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.928194867886179</v>
+      <c r="M12" t="n">
+        <v>26.96800595238095</v>
+      </c>
+      <c r="N12" t="n">
+        <v>14.66703869047619</v>
+      </c>
+      <c r="O12" t="n">
+        <v>12.73065476190476</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>6.240699404761904</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4.200148809523809</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.38764880952381</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>3.658854166666667</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.736742424242424</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AK12" s="2" t="n">
+        <v>27.78197216386554</v>
       </c>
     </row>
     <row r="13">
@@ -1007,17 +1529,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>11.58804283164783</v>
+        <v>4417.120181405895</v>
       </c>
       <c r="D13" t="n">
-        <v>20.78447694894744</v>
+        <v>405.7921690032596</v>
       </c>
       <c r="E13" t="n">
-        <v>14.54040041202452</v>
+        <v>283.8840080442882</v>
       </c>
       <c r="F13" t="n">
         <v>1.429429476492218</v>
@@ -1026,16 +1548,57 @@
         <v>0.3370868077514558</v>
       </c>
       <c r="H13" t="n">
+        <v>16</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.515997023809524</v>
+      </c>
+      <c r="J13" t="n">
+        <v>27.91480654761905</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5.548851376488095</v>
+      </c>
+      <c r="L13" t="n">
         <v>2</v>
       </c>
-      <c r="I13" t="n">
-        <v>0.7658155487804879</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1.429782774390244</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1.097799161585366</v>
+      <c r="M13" t="n">
+        <v>27.91480654761905</v>
+      </c>
+      <c r="N13" t="n">
+        <v>14.9516369047619</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>6.32626488095238</v>
+      </c>
+      <c r="U13" t="n">
+        <v>5.777529761904762</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.515997023809524</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>3.802083333333333</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.817615327380953</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AK13" s="2" t="n">
+        <v>15.51864495798319</v>
       </c>
     </row>
     <row r="14">
@@ -1046,17 +1609,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>11.48423557406306</v>
+        <v>4377.551020408163</v>
       </c>
       <c r="D14" t="n">
-        <v>20.91653093477575</v>
+        <v>408.3703658694312</v>
       </c>
       <c r="E14" t="n">
-        <v>14.46896298920236</v>
+        <v>282.4892774082365</v>
       </c>
       <c r="F14" t="n">
         <v>1.445613687061399</v>
@@ -1065,16 +1628,60 @@
         <v>0.329862269089616</v>
       </c>
       <c r="H14" t="n">
+        <v>16</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.452752976190476</v>
+      </c>
+      <c r="J14" t="n">
+        <v>30.05022321428571</v>
+      </c>
+      <c r="K14" t="n">
+        <v>6.081426711309524</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" t="n">
+        <v>30.05022321428571</v>
+      </c>
+      <c r="N14" t="n">
+        <v>15.12090773809524</v>
+      </c>
+      <c r="S14" t="n">
         <v>3</v>
       </c>
-      <c r="I14" t="n">
-        <v>0.5365853658536586</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.539157774390244</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.9500762195121952</v>
+      <c r="T14" t="n">
+        <v>10.47619047619048</v>
+      </c>
+      <c r="U14" t="n">
+        <v>5.822172619047619</v>
+      </c>
+      <c r="V14" t="n">
+        <v>5.167410714285714</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.452752976190476</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>3.772321428571428</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.787811147186147</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>Primary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AK14" s="2" t="n">
+        <v>13.83965773809523</v>
       </c>
     </row>
     <row r="15">
@@ -1085,17 +1692,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>11.46073765615705</v>
+        <v>4368.594104308389</v>
       </c>
       <c r="D15" t="n">
-        <v>20.45484965603526</v>
+        <v>399.3565885225931</v>
       </c>
       <c r="E15" t="n">
-        <v>14.29404657352261</v>
+        <v>279.0742426259177</v>
       </c>
       <c r="F15" t="n">
         <v>1.431004827836823</v>
@@ -1104,16 +1711,60 @@
         <v>0.3442150475669623</v>
       </c>
       <c r="H15" t="n">
+        <v>16</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.238839285714286</v>
+      </c>
+      <c r="J15" t="n">
+        <v>27.19680059523809</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5.849725632440476</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M15" t="n">
+        <v>27.19680059523809</v>
+      </c>
+      <c r="N15" t="n">
+        <v>15.89285714285714</v>
+      </c>
+      <c r="S15" t="n">
         <v>3</v>
       </c>
-      <c r="I15" t="n">
-        <v>0.5365853658536586</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1.393006859756098</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.9145388719512195</v>
+      <c r="T15" t="n">
+        <v>10.47619047619048</v>
+      </c>
+      <c r="U15" t="n">
+        <v>5.64360119047619</v>
+      </c>
+      <c r="V15" t="n">
+        <v>5.368303571428571</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.238839285714286</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>3.962053571428571</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.637987012987012</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>Primary_min_mm</t>
+        </is>
+      </c>
+      <c r="AK15" s="2" t="n">
+        <v>14.26525297619047</v>
       </c>
     </row>
     <row r="16">
@@ -1124,17 +1775,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>11.42920880428317</v>
+        <v>4356.57596371882</v>
       </c>
       <c r="D16" t="n">
-        <v>20.87223253308273</v>
+        <v>407.5054923125675</v>
       </c>
       <c r="E16" t="n">
-        <v>14.21077310166708</v>
+        <v>277.4484272230239</v>
       </c>
       <c r="F16" t="n">
         <v>1.468761226694569</v>
@@ -1143,16 +1794,60 @@
         <v>0.3296766755214937</v>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5207698170731707</v>
+        <v>1.25</v>
       </c>
       <c r="J16" t="n">
-        <v>1.501810213414634</v>
+        <v>29.32105654761905</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9438833841463415</v>
+        <v>6.098051525297619</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>29.32105654761905</v>
+      </c>
+      <c r="N16" t="n">
+        <v>15.79613095238095</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4</v>
+      </c>
+      <c r="W16" t="n">
+        <v>5.455729166666666</v>
+      </c>
+      <c r="X16" t="n">
+        <v>10.16741071428571</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>6.757347470238095</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>3.889508928571428</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.542224702380953</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>Primary_max_mm</t>
+        </is>
+      </c>
+      <c r="AK16" s="2" t="n">
+        <v>24.86917162698412</v>
       </c>
     </row>
     <row r="17">
@@ -1163,35 +1858,79 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>11.38518738845925</v>
+        <v>4339.795918367347</v>
       </c>
       <c r="D17" t="n">
-        <v>20.70221880587136</v>
+        <v>404.1861766860599</v>
       </c>
       <c r="E17" t="n">
-        <v>14.12158153987512</v>
+        <v>275.7070681594667</v>
       </c>
       <c r="F17" t="n">
         <v>1.465998602735429</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3338230019197311</v>
+        <v>0.3338230019197312</v>
       </c>
       <c r="H17" t="n">
+        <v>15</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.370907738095238</v>
+      </c>
+      <c r="J17" t="n">
+        <v>31.51041666666666</v>
+      </c>
+      <c r="K17" t="n">
+        <v>6.341393849206349</v>
+      </c>
+      <c r="L17" t="n">
         <v>2</v>
       </c>
-      <c r="I17" t="n">
-        <v>0.7956364329268293</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1.613948170731707</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1.204792301829268</v>
+      <c r="M17" t="n">
+        <v>31.51041666666666</v>
+      </c>
+      <c r="N17" t="n">
+        <v>15.53385416666667</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4</v>
+      </c>
+      <c r="W17" t="n">
+        <v>5.379464285714286</v>
+      </c>
+      <c r="X17" t="n">
+        <v>6.432291666666666</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>5.980282738095237</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.370907738095238</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>3.751860119047619</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.683945105820106</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>Primary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AK17" s="2" t="n">
+        <v>17.64725942460317</v>
       </c>
     </row>
     <row r="18">
@@ -1202,17 +1941,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>11.21326591314694</v>
+        <v>4274.263038548753</v>
       </c>
       <c r="D18" t="n">
-        <v>20.63323278252671</v>
+        <v>402.8393067064739</v>
       </c>
       <c r="E18" t="n">
-        <v>13.90278731032116</v>
+        <v>271.4353712967464</v>
       </c>
       <c r="F18" t="n">
         <v>1.484107634100754</v>
@@ -1221,16 +1960,60 @@
         <v>0.3309843271613768</v>
       </c>
       <c r="H18" t="n">
+        <v>14</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.915922619047619</v>
+      </c>
+      <c r="J18" t="n">
+        <v>32.85714285714285</v>
+      </c>
+      <c r="K18" t="n">
+        <v>6.591331845238094</v>
+      </c>
+      <c r="L18" t="n">
         <v>2</v>
       </c>
-      <c r="I18" t="n">
-        <v>0.8374618902439025</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1.682926829268293</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1.260194359756098</v>
+      <c r="M18" t="n">
+        <v>32.85714285714285</v>
+      </c>
+      <c r="N18" t="n">
+        <v>16.35044642857143</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4</v>
+      </c>
+      <c r="W18" t="n">
+        <v>4.867931547619047</v>
+      </c>
+      <c r="X18" t="n">
+        <v>5.422247023809524</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>5.115792410714286</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.915922619047619</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>3.735119047619047</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.825985863095238</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="AK18" s="2" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="19">
@@ -1241,35 +2024,79 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>11.12611540749554</v>
+        <v>4241.043083900227</v>
       </c>
       <c r="D19" t="n">
-        <v>20.55342599822254</v>
+        <v>401.2811742510114</v>
       </c>
       <c r="E19" t="n">
-        <v>13.85992489209989</v>
+        <v>270.5985336076645</v>
       </c>
       <c r="F19" t="n">
         <v>1.482939204810404</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3309672161965058</v>
+        <v>0.3309672161965059</v>
       </c>
       <c r="H19" t="n">
+        <v>13</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.490699404761905</v>
+      </c>
+      <c r="J19" t="n">
+        <v>33.61049107142857</v>
+      </c>
+      <c r="K19" t="n">
+        <v>6.931232829670327</v>
+      </c>
+      <c r="L19" t="n">
         <v>2</v>
       </c>
-      <c r="I19" t="n">
-        <v>0.8492759146341464</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1.721512957317073</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1.28539443597561</v>
+      <c r="M19" t="n">
+        <v>33.61049107142857</v>
+      </c>
+      <c r="N19" t="n">
+        <v>16.58110119047619</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4</v>
+      </c>
+      <c r="W19" t="n">
+        <v>4.159226190476191</v>
+      </c>
+      <c r="X19" t="n">
+        <v>5.09672619047619</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>4.675409226190476</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.490699404761905</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>3.645833333333333</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>3.030399659863946</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AK19" s="2" t="n">
+        <v>9.056222098214285</v>
       </c>
     </row>
     <row r="20">
@@ -1280,17 +2107,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>11.03628792385485</v>
+        <v>4206.802721088435</v>
       </c>
       <c r="D20" t="n">
-        <v>20.1227710392417</v>
+        <v>392.8731488613855</v>
       </c>
       <c r="E20" t="n">
-        <v>13.77665139698401</v>
+        <v>268.9727177506401</v>
       </c>
       <c r="F20" t="n">
         <v>1.460643117067402</v>
@@ -1299,16 +2126,60 @@
         <v>0.3424974281985812</v>
       </c>
       <c r="H20" t="n">
+        <v>13</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.946428571428571</v>
+      </c>
+      <c r="J20" t="n">
+        <v>28.39285714285714</v>
+      </c>
+      <c r="K20" t="n">
+        <v>6.731913919413921</v>
+      </c>
+      <c r="L20" t="n">
         <v>2</v>
       </c>
-      <c r="I20" t="n">
-        <v>0.9162538109756098</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1.454268292682927</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1.185261051829268</v>
+      <c r="M20" t="n">
+        <v>28.39285714285714</v>
+      </c>
+      <c r="N20" t="n">
+        <v>17.88876488095238</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4</v>
+      </c>
+      <c r="W20" t="n">
+        <v>3.989955357142857</v>
+      </c>
+      <c r="X20" t="n">
+        <v>5.470610119047619</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>4.475446428571428</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.946428571428571</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>3.824404761904762</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>3.333067602040817</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AK20" s="2" t="n">
+        <v>5.358382936507937</v>
       </c>
     </row>
     <row r="21">
@@ -1319,35 +2190,79 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>10.93486020226056</v>
+        <v>4168.140589569161</v>
       </c>
       <c r="D21" t="n">
-        <v>20.54750790537857</v>
+        <v>401.1656305335817</v>
       </c>
       <c r="E21" t="n">
-        <v>13.7195015331594</v>
+        <v>267.8569346950168</v>
       </c>
       <c r="F21" t="n">
-        <v>1.497686184568455</v>
+        <v>1.497686184568456</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3254653707142177</v>
+        <v>0.3254653707142176</v>
       </c>
       <c r="H21" t="n">
+        <v>14</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.767857142857143</v>
+      </c>
+      <c r="J21" t="n">
+        <v>27.72321428571428</v>
+      </c>
+      <c r="K21" t="n">
+        <v>6.719015731292517</v>
+      </c>
+      <c r="L21" t="n">
         <v>2</v>
       </c>
-      <c r="I21" t="n">
-        <v>0.9373094512195123</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1.419969512195122</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1.178639481707317</v>
+      <c r="M21" t="n">
+        <v>27.72321428571428</v>
+      </c>
+      <c r="N21" t="n">
+        <v>18.29985119047619</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="W21" t="n">
+        <v>4.047619047619047</v>
+      </c>
+      <c r="X21" t="n">
+        <v>5.7421875</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>4.619419642857142</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.767857142857143</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>3.921130952380952</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>3.563722363945578</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AK21" s="2" t="n">
+        <v>5.267857142857142</v>
       </c>
     </row>
     <row r="22">
@@ -1357,7 +2272,15 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="AK22" s="2" t="n">
+        <v>4.587673611111111</v>
       </c>
     </row>
     <row r="23">
@@ -1371,6 +2294,14 @@
           <t>mm</t>
         </is>
       </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="AK23" s="2" t="n">
+        <v>8.547402033730156</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1380,6 +2311,120 @@
       </c>
       <c r="B24" t="n">
         <v>25</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AK24" s="2" t="n">
+        <v>6.00348255621693</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ScalebarMeasuredPixels:</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AK25" s="2" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldLength:</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AK26" s="2" t="n">
+        <v>3.394717261904762</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldUnit:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AK27" s="2" t="n">
+        <v>2.922712053571428</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AK28" s="2" t="n">
+        <v>2.445436507936508</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AK29" s="2" t="n">
+        <v>1.680036272321428</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AK30" s="2" t="n">
+        <v>3.77836681547619</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AK31" s="2" t="n">
+        <v>2.858879299579286</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AK32" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/measurements/33/Filled_2D_sections/axial/week33_axial_Batch_Allmarks.xlsx
+++ b/measurements/33/Filled_2D_sections/axial/week33_axial_Batch_Allmarks.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -137,6 +138,211 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2430,4 +2636,1277 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Workbook Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>week33_axial_Batch_Allmarks.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>axial</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Slice rows analyzed</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When a sulcus class count exceeds 3, approximate raw sulcus values are reconstructed from count + min/max/mean for summary stats and boxplots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Core Metric Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4294.801587301587</v>
+      </c>
+      <c r="D10" t="n">
+        <v>83.8023969351125</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4168.140589569161</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4419.160997732426</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>perimeter</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>440.5259672942615</v>
+      </c>
+      <c r="D11" t="n">
+        <v>39.72146814025505</v>
+      </c>
+      <c r="E11" t="n">
+        <v>392.8731488613855</v>
+      </c>
+      <c r="F11" t="n">
+        <v>508.7962910674867</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LGI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.56005955253642</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.1090423970575815</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.429429476492218</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.763698921053586</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Compactness</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.2847204675368405</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.0510817079065982</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.2049406409111947</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.3442150475669623</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Counts Per Slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sulci_count</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>band_axis2_s00_idx0152.png</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>11</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>11</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>6</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>band_axis2_s01_idx0154.png</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>10</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>10</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>6</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>band_axis2_s02_idx0155.png</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>10</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>10</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>band_axis2_s03_idx0156.png</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>10</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>10</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>band_axis2_s04_idx0158.png</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>12</v>
+      </c>
+      <c r="C21" t="n">
+        <v>4</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>6</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>12</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" t="n">
+        <v>6</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>band_axis2_s05_idx0159.png</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>12</v>
+      </c>
+      <c r="C22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>7</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>12</v>
+      </c>
+      <c r="H22" t="n">
+        <v>4</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>7</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>band_axis2_s06_idx0160.png</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>12</v>
+      </c>
+      <c r="C23" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>7</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>12</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>7</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>band_axis2_s07_idx0161.png</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>13</v>
+      </c>
+      <c r="C24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>8</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>13</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" t="n">
+        <v>8</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>band_axis2_s08_idx0163.png</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>15</v>
+      </c>
+      <c r="C25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" t="n">
+        <v>4</v>
+      </c>
+      <c r="E25" t="n">
+        <v>8</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>15</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I25" t="n">
+        <v>4</v>
+      </c>
+      <c r="J25" t="n">
+        <v>8</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>band_axis2_s09_idx0164.png</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>17</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="n">
+        <v>5</v>
+      </c>
+      <c r="E26" t="n">
+        <v>10</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>17</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" t="n">
+        <v>5</v>
+      </c>
+      <c r="J26" t="n">
+        <v>10</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>band_axis2_s10_idx0165.png</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>16</v>
+      </c>
+      <c r="C27" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>11</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>16</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" t="n">
+        <v>11</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>band_axis2_s11_idx0166.png</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>16</v>
+      </c>
+      <c r="C28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>12</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>16</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" t="n">
+        <v>12</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>band_axis2_s12_idx0168.png</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>16</v>
+      </c>
+      <c r="C29" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" t="n">
+        <v>11</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>16</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2</v>
+      </c>
+      <c r="I29" t="n">
+        <v>3</v>
+      </c>
+      <c r="J29" t="n">
+        <v>11</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>band_axis2_s13_idx0169.png</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>16</v>
+      </c>
+      <c r="C30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" t="n">
+        <v>11</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>16</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" t="n">
+        <v>3</v>
+      </c>
+      <c r="J30" t="n">
+        <v>11</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>band_axis2_s14_idx0170.png</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>16</v>
+      </c>
+      <c r="C31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" t="n">
+        <v>4</v>
+      </c>
+      <c r="E31" t="n">
+        <v>10</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>16</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" t="n">
+        <v>4</v>
+      </c>
+      <c r="J31" t="n">
+        <v>10</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>band_axis2_s15_idx0171.png</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>15</v>
+      </c>
+      <c r="C32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" t="n">
+        <v>4</v>
+      </c>
+      <c r="E32" t="n">
+        <v>9</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>15</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" t="n">
+        <v>4</v>
+      </c>
+      <c r="J32" t="n">
+        <v>9</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>band_axis2_s16_idx0173.png</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>14</v>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="n">
+        <v>4</v>
+      </c>
+      <c r="E33" t="n">
+        <v>8</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>14</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" t="n">
+        <v>4</v>
+      </c>
+      <c r="J33" t="n">
+        <v>8</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>band_axis2_s17_idx0174.png</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>13</v>
+      </c>
+      <c r="C34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" t="n">
+        <v>4</v>
+      </c>
+      <c r="E34" t="n">
+        <v>7</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>13</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" t="n">
+        <v>4</v>
+      </c>
+      <c r="J34" t="n">
+        <v>7</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>band_axis2_s18_idx0175.png</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>13</v>
+      </c>
+      <c r="C35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" t="n">
+        <v>4</v>
+      </c>
+      <c r="E35" t="n">
+        <v>7</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>13</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2</v>
+      </c>
+      <c r="I35" t="n">
+        <v>4</v>
+      </c>
+      <c r="J35" t="n">
+        <v>7</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>band_axis2_s19_idx0176.png</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>14</v>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="n">
+        <v>5</v>
+      </c>
+      <c r="E36" t="n">
+        <v>7</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>14</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2</v>
+      </c>
+      <c r="I36" t="n">
+        <v>5</v>
+      </c>
+      <c r="J36" t="n">
+        <v>7</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Count Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2.282081229238369</v>
+      </c>
+      <c r="E40" t="n">
+        <v>10</v>
+      </c>
+      <c r="F40" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.7591546545162482</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>20</v>
+      </c>
+      <c r="C42" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1.468977445995038</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C43" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2.964704653791086</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>20</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sulcus Value Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>primary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>51</v>
+      </c>
+      <c r="C48" t="n">
+        <v>19.94266456582633</v>
+      </c>
+      <c r="D48" t="n">
+        <v>6.319486951395612</v>
+      </c>
+      <c r="E48" t="n">
+        <v>12.73065476190476</v>
+      </c>
+      <c r="F48" t="n">
+        <v>33.61049107142857</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>secondary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>70</v>
+      </c>
+      <c r="C49" t="n">
+        <v>6.332987882653061</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2.204693573785195</v>
+      </c>
+      <c r="E49" t="n">
+        <v>3.989955357142857</v>
+      </c>
+      <c r="F49" t="n">
+        <v>12.50930059523809</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tertiary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>150</v>
+      </c>
+      <c r="C50" t="n">
+        <v>2.836954365079365</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.5907694799494111</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.238839285714286</v>
+      </c>
+      <c r="F50" t="n">
+        <v>4.109002976190476</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>unclassified_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>